--- a/Test Plan Document.xlsx
+++ b/Test Plan Document.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17FF5D02-6735-4016-B80A-90EE70DFFAF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{260A03D3-A034-487C-B5D3-58BCC90364C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -262,7 +262,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="160">
   <si>
     <t>Field</t>
   </si>
@@ -736,6 +736,12 @@
   </si>
   <si>
     <t>Invalid Address</t>
+  </si>
+  <si>
+    <t>Address should not be saved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Done as expected </t>
   </si>
 </sst>
 </file>
@@ -2011,55 +2017,6 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2074,6 +2031,55 @@
     </xf>
     <xf numFmtId="0" fontId="37" fillId="8" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
@@ -2355,15 +2361,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1">
-      <c r="B1" s="82" t="s">
+      <c r="B1" s="89" t="s">
         <v>133</v>
       </c>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="84"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="90"/>
+      <c r="F1" s="90"/>
+      <c r="G1" s="90"/>
+      <c r="H1" s="91"/>
     </row>
     <row r="2" spans="1:8" ht="22.5" customHeight="1">
       <c r="B2" s="1" t="s">
@@ -2372,12 +2378,12 @@
       <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="85" t="s">
+      <c r="E2" s="92" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="86"/>
-      <c r="G2" s="86"/>
-      <c r="H2" s="87"/>
+      <c r="F2" s="93"/>
+      <c r="G2" s="93"/>
+      <c r="H2" s="94"/>
     </row>
     <row r="3" spans="1:8" ht="19.5" customHeight="1">
       <c r="B3" s="3" t="s">
@@ -2407,12 +2413,10 @@
         <v>10</v>
       </c>
       <c r="E4" s="11">
-        <f>COUNTA(A14:A21)</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F4" s="14">
-        <f>COUNTIF(H14:H21, "Passed")</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G4" s="15">
         <f>COUNTIF(H14:H21, "Failed")</f>
@@ -2482,10 +2486,10 @@
       <c r="C8" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="88"/>
-      <c r="F8" s="89"/>
-      <c r="G8" s="89"/>
-      <c r="H8" s="89"/>
+      <c r="E8" s="95"/>
+      <c r="F8" s="96"/>
+      <c r="G8" s="96"/>
+      <c r="H8" s="96"/>
     </row>
     <row r="9" spans="1:8" ht="19.5" customHeight="1">
       <c r="B9" s="3" t="s">
@@ -2494,10 +2498,10 @@
       <c r="C9" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="90"/>
-      <c r="F9" s="89"/>
-      <c r="G9" s="89"/>
-      <c r="H9" s="89"/>
+      <c r="E9" s="97"/>
+      <c r="F9" s="96"/>
+      <c r="G9" s="96"/>
+      <c r="H9" s="96"/>
     </row>
     <row r="10" spans="1:8" ht="21" customHeight="1">
       <c r="B10" s="3" t="s">
@@ -2524,10 +2528,10 @@
       <c r="H11" s="32"/>
     </row>
     <row r="12" spans="1:8" ht="21" customHeight="1">
-      <c r="E12" s="91"/>
-      <c r="F12" s="89"/>
-      <c r="G12" s="89"/>
-      <c r="H12" s="89"/>
+      <c r="E12" s="98"/>
+      <c r="F12" s="96"/>
+      <c r="G12" s="96"/>
+      <c r="H12" s="96"/>
     </row>
     <row r="13" spans="1:8" ht="27" customHeight="1">
       <c r="A13" s="41" t="s">
@@ -2764,92 +2768,107 @@
       </c>
     </row>
     <row r="22" spans="1:8" ht="27" customHeight="1">
-      <c r="A22" s="107" t="s">
+      <c r="A22" s="82" t="s">
         <v>138</v>
       </c>
-      <c r="B22" s="108" t="s">
+      <c r="B22" s="83" t="s">
         <v>139</v>
       </c>
-      <c r="C22" s="110" t="s">
+      <c r="C22" s="85" t="s">
         <v>140</v>
       </c>
-      <c r="D22" s="110" t="s">
+      <c r="D22" s="85" t="s">
         <v>141</v>
       </c>
-      <c r="E22" s="110" t="s">
+      <c r="E22" s="85" t="s">
         <v>61</v>
       </c>
-      <c r="F22" s="110" t="s">
+      <c r="F22" s="85" t="s">
         <v>142</v>
       </c>
-      <c r="G22" s="111" t="s">
+      <c r="G22" s="86" t="s">
         <v>46</v>
       </c>
-      <c r="H22" s="112" t="s">
+      <c r="H22" s="87" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="25.8" customHeight="1">
-      <c r="A24" s="107" t="s">
+      <c r="A24" s="82" t="s">
         <v>143</v>
       </c>
-      <c r="B24" s="108" t="s">
+      <c r="B24" s="83" t="s">
         <v>144</v>
       </c>
-      <c r="C24" s="113" t="s">
+      <c r="C24" s="88" t="s">
         <v>145</v>
       </c>
-      <c r="D24" s="109" t="s">
+      <c r="D24" s="84" t="s">
         <v>146</v>
       </c>
-      <c r="E24" s="109" t="s">
+      <c r="E24" s="84" t="s">
         <v>147</v>
       </c>
-      <c r="F24" s="109" t="s">
+      <c r="F24" s="84" t="s">
         <v>148</v>
       </c>
-      <c r="G24" s="114" t="s">
+      <c r="G24" s="84" t="s">
         <v>153</v>
       </c>
+      <c r="H24" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="26" spans="1:8" ht="28.8" customHeight="1">
-      <c r="A26" s="107" t="s">
+      <c r="A26" s="82" t="s">
         <v>149</v>
       </c>
-      <c r="B26" s="108" t="s">
+      <c r="B26" s="83" t="s">
         <v>144</v>
       </c>
-      <c r="C26" s="109" t="s">
+      <c r="C26" s="84" t="s">
         <v>150</v>
       </c>
-      <c r="D26" s="109" t="s">
+      <c r="D26" s="84" t="s">
         <v>151</v>
       </c>
-      <c r="E26" s="109" t="s">
+      <c r="E26" s="84" t="s">
         <v>147</v>
       </c>
-      <c r="F26" s="109" t="s">
+      <c r="F26" s="84" t="s">
         <v>152</v>
       </c>
       <c r="G26" t="s">
         <v>153</v>
       </c>
+      <c r="H26" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="27" spans="1:8" ht="29.4" customHeight="1">
-      <c r="A27" s="107" t="s">
+      <c r="A27" s="82" t="s">
         <v>154</v>
       </c>
-      <c r="B27" s="108" t="s">
+      <c r="B27" s="83" t="s">
         <v>144</v>
       </c>
-      <c r="C27" s="114" t="s">
+      <c r="C27" s="84" t="s">
         <v>155</v>
       </c>
-      <c r="D27" s="109" t="s">
+      <c r="D27" s="84" t="s">
         <v>156</v>
       </c>
-      <c r="E27" s="114" t="s">
+      <c r="E27" s="84" t="s">
         <v>157</v>
+      </c>
+      <c r="F27" s="114" t="s">
+        <v>158</v>
+      </c>
+      <c r="G27" s="114" t="s">
+        <v>159</v>
+      </c>
+      <c r="H27" s="114" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -2891,42 +2910,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="31.5" customHeight="1">
-      <c r="A1" s="100" t="s">
+      <c r="A1" s="106" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="101"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="102"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="108"/>
     </row>
     <row r="2" spans="1:8" ht="21" customHeight="1">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="103" t="s">
+      <c r="B2" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="104"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="106" t="s">
+      <c r="C2" s="110"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="112" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="104"/>
-      <c r="G2" s="104"/>
-      <c r="H2" s="105"/>
+      <c r="F2" s="110"/>
+      <c r="G2" s="110"/>
+      <c r="H2" s="111"/>
     </row>
     <row r="3" spans="1:8" ht="18" customHeight="1">
       <c r="A3" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="92" t="s">
+      <c r="B3" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="93"/>
-      <c r="D3" s="94"/>
+      <c r="C3" s="100"/>
+      <c r="D3" s="101"/>
       <c r="E3" s="10" t="s">
         <v>4</v>
       </c>
@@ -2944,11 +2963,11 @@
       <c r="A4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="92" t="s">
+      <c r="B4" s="99" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="93"/>
-      <c r="D4" s="94"/>
+      <c r="C4" s="100"/>
+      <c r="D4" s="101"/>
       <c r="E4" s="16">
         <f>COUNTA(A14:A23)</f>
         <v>10</v>
@@ -2970,11 +2989,11 @@
       <c r="A5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="92" t="s">
+      <c r="B5" s="99" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="93"/>
-      <c r="D5" s="94"/>
+      <c r="C5" s="100"/>
+      <c r="D5" s="101"/>
       <c r="E5" s="10" t="s">
         <v>14</v>
       </c>
@@ -2992,11 +3011,11 @@
       <c r="A6" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="92" t="s">
+      <c r="B6" s="99" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="93"/>
-      <c r="D6" s="94"/>
+      <c r="C6" s="100"/>
+      <c r="D6" s="101"/>
       <c r="E6" s="22">
         <f>COUNTIF(H14:H23, "Blocked")</f>
         <v>0</v>
@@ -3018,11 +3037,11 @@
       <c r="A7" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="92" t="s">
+      <c r="B7" s="99" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="93"/>
-      <c r="D7" s="94"/>
+      <c r="C7" s="100"/>
+      <c r="D7" s="101"/>
       <c r="E7" s="28"/>
       <c r="F7" s="28"/>
       <c r="G7" s="28"/>
@@ -3032,39 +3051,39 @@
       <c r="A8" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="92" t="s">
+      <c r="B8" s="99" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="93"/>
-      <c r="D8" s="94"/>
-      <c r="E8" s="88"/>
-      <c r="F8" s="89"/>
-      <c r="G8" s="89"/>
-      <c r="H8" s="89"/>
+      <c r="C8" s="100"/>
+      <c r="D8" s="101"/>
+      <c r="E8" s="95"/>
+      <c r="F8" s="96"/>
+      <c r="G8" s="96"/>
+      <c r="H8" s="96"/>
     </row>
     <row r="9" spans="1:8" ht="19.5" customHeight="1">
       <c r="A9" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="92" t="s">
+      <c r="B9" s="99" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="93"/>
-      <c r="D9" s="94"/>
-      <c r="E9" s="95"/>
-      <c r="F9" s="89"/>
-      <c r="G9" s="89"/>
-      <c r="H9" s="89"/>
+      <c r="C9" s="100"/>
+      <c r="D9" s="101"/>
+      <c r="E9" s="113"/>
+      <c r="F9" s="96"/>
+      <c r="G9" s="96"/>
+      <c r="H9" s="96"/>
     </row>
     <row r="10" spans="1:8" ht="19.5" customHeight="1">
       <c r="A10" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="92" t="s">
+      <c r="B10" s="99" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="93"/>
-      <c r="D10" s="94"/>
+      <c r="C10" s="100"/>
+      <c r="D10" s="101"/>
       <c r="E10" s="30"/>
       <c r="F10" s="34"/>
       <c r="G10" s="35"/>
@@ -3074,9 +3093,9 @@
       <c r="A11" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="96"/>
-      <c r="C11" s="97"/>
-      <c r="D11" s="98"/>
+      <c r="B11" s="102"/>
+      <c r="C11" s="103"/>
+      <c r="D11" s="104"/>
       <c r="E11" s="39"/>
       <c r="F11" s="34"/>
       <c r="G11" s="42"/>
@@ -3087,10 +3106,10 @@
       <c r="B12" s="44"/>
       <c r="C12" s="44"/>
       <c r="D12" s="44"/>
-      <c r="E12" s="99"/>
-      <c r="F12" s="89"/>
-      <c r="G12" s="89"/>
-      <c r="H12" s="89"/>
+      <c r="E12" s="105"/>
+      <c r="F12" s="96"/>
+      <c r="G12" s="96"/>
+      <c r="H12" s="96"/>
     </row>
     <row r="13" spans="1:8" ht="24" customHeight="1">
       <c r="A13" s="49" t="s">
